--- a/rules/CORE-000779/positive/01/data/unit-test-coreid-CG0376-positive.xlsx
+++ b/rules/CORE-000779/positive/01/data/unit-test-coreid-CG0376-positive.xlsx
@@ -1,50 +1,171 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000779\positive\01\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F692000C-B486-44C6-8C98-090DC0576847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="31440" yWindow="2640" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="td.xpt" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="td.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>td.xpt</t>
+  </si>
+  <si>
+    <t>Trial Disease Assessments</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>TDORDER</t>
+  </si>
+  <si>
+    <t>TDANCVAR</t>
+  </si>
+  <si>
+    <t>TDSTOFF</t>
+  </si>
+  <si>
+    <t>TDTGTPAI</t>
+  </si>
+  <si>
+    <t>TDMINPAI</t>
+  </si>
+  <si>
+    <t>TDMAXPAI</t>
+  </si>
+  <si>
+    <t>TDNUMRPT</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Sequence of Planned Assessment Schedule</t>
+  </si>
+  <si>
+    <t>Anchor Variable Name</t>
+  </si>
+  <si>
+    <t>Offset from the Anchor</t>
+  </si>
+  <si>
+    <t>Planned Assessment Interval</t>
+  </si>
+  <si>
+    <t>Planned Assessment Interval Minimum</t>
+  </si>
+  <si>
+    <t>Planned Assessment Interval Maximum</t>
+  </si>
+  <si>
+    <t>Maximum Number of Actual Assessments</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISC-PILOT</t>
+  </si>
+  <si>
+    <t>TD</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>P0D</t>
+  </si>
+  <si>
+    <t>P12W</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>P2Y</t>
+  </si>
+  <si>
+    <t>P0005D</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <i val="1"/>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
-        <bgColor rgb="00FFFFCC"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,91 +197,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -448,36 +510,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -486,36 +536,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>td.xpt</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Trial Disease Assessments</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -524,226 +562,194 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>STUDYID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>DOMAIN</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>TDORDER</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>TDANCVAR</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>TDSTOFF</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>TDTGTPAI</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>TDMINPAI</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>TDMAXPAI</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>TDNUMRPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Study Identifier</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Domain Abbreviation</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Sequence of Planned Assessment Schedule</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Anchor Variable Name</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Offset from the Anchor</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Planned Assessment Interval</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Planned Assessment Interval Minimum</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Planned Assessment Interval Maximum</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Maximum Number of Actual Assessments</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>50</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="4">
         <v>50</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="4">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>50</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="4">
         <v>50</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="4">
         <v>50</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="4">
         <v>50</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="4">
         <v>50</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>CDISC-PILOT</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>P0D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>CDISC-PILOT</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>P12W</t>
-        </is>
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/rules/CORE-000779/positive/01/data/unit-test-coreid-CG0376-positive.xlsx
+++ b/rules/CORE-000779/positive/01/data/unit-test-coreid-CG0376-positive.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000779\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F692000C-B486-44C6-8C98-090DC0576847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75108F1B-43A2-4006-97C8-6A9D74EAD6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31440" yWindow="2640" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30765" yWindow="1800" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
   <si>
     <t>Product</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>P0005D</t>
+  </si>
+  <si>
+    <t>PT1H</t>
   </si>
 </sst>
 </file>
@@ -563,7 +566,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -752,6 +755,20 @@
         <v>35</v>
       </c>
     </row>
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
